--- a/Dr. Peris/Tharaka_Reference_Labelling_Workbook.xlsx
+++ b/Dr. Peris/Tharaka_Reference_Labelling_Workbook.xlsx
@@ -764,7 +764,7 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>37.8924310725676</v>
+        <v>37.8924310725672</v>
       </c>
       <c r="C7" t="n">
         <v>0.00419338370937894</v>
@@ -816,7 +816,7 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>38.0919450804004</v>
+        <v>38.0919450803861</v>
       </c>
       <c r="C9" t="n">
         <v>0.0207313021641273</v>
@@ -946,7 +946,7 @@
         <v>21</v>
       </c>
       <c r="B14" t="n">
-        <v>38.2883911294841</v>
+        <v>38.2883911294605</v>
       </c>
       <c r="C14" t="n">
         <v>-0.0472074421045568</v>
@@ -1024,7 +1024,7 @@
         <v>24</v>
       </c>
       <c r="B17" t="n">
-        <v>37.9538767889898</v>
+        <v>37.9538767891863</v>
       </c>
       <c r="C17" t="n">
         <v>-0.0195524953341902</v>
@@ -1180,7 +1180,7 @@
         <v>30</v>
       </c>
       <c r="B23" t="n">
-        <v>37.9296323330166</v>
+        <v>37.9296323330092</v>
       </c>
       <c r="C23" t="n">
         <v>-0.40076065151247</v>
@@ -1284,7 +1284,7 @@
         <v>34</v>
       </c>
       <c r="B27" t="n">
-        <v>38.1358611378785</v>
+        <v>38.1358611378717</v>
       </c>
       <c r="C27" t="n">
         <v>-0.0719145881400765</v>
@@ -1440,7 +1440,7 @@
         <v>40</v>
       </c>
       <c r="B33" t="n">
-        <v>38.0343956381725</v>
+        <v>38.0343956381619</v>
       </c>
       <c r="C33" t="n">
         <v>-0.14452857309233</v>
@@ -1518,7 +1518,7 @@
         <v>43</v>
       </c>
       <c r="B36" t="n">
-        <v>37.9617269046748</v>
+        <v>37.9617269046535</v>
       </c>
       <c r="C36" t="n">
         <v>-0.32083570613195</v>
@@ -1544,7 +1544,7 @@
         <v>44</v>
       </c>
       <c r="B37" t="n">
-        <v>38.0162606459222</v>
+        <v>38.0162606458934</v>
       </c>
       <c r="C37" t="n">
         <v>-0.191797476890575</v>
@@ -1570,7 +1570,7 @@
         <v>45</v>
       </c>
       <c r="B38" t="n">
-        <v>38.1637475437495</v>
+        <v>38.1637475437615</v>
       </c>
       <c r="C38" t="n">
         <v>-0.186084816531836</v>
@@ -1596,7 +1596,7 @@
         <v>46</v>
       </c>
       <c r="B39" t="n">
-        <v>38.1155711122823</v>
+        <v>38.1155711122832</v>
       </c>
       <c r="C39" t="n">
         <v>-0.226560786650188</v>
@@ -1648,7 +1648,7 @@
         <v>48</v>
       </c>
       <c r="B41" t="n">
-        <v>38.1808170161058</v>
+        <v>38.1808170161056</v>
       </c>
       <c r="C41" t="n">
         <v>-0.156907838031614</v>
@@ -1700,7 +1700,7 @@
         <v>50</v>
       </c>
       <c r="B43" t="n">
-        <v>37.9445030838813</v>
+        <v>37.9445030838717</v>
       </c>
       <c r="C43" t="n">
         <v>-0.0610734753287546</v>
@@ -1778,7 +1778,7 @@
         <v>53</v>
       </c>
       <c r="B46" t="n">
-        <v>38.0925354254433</v>
+        <v>38.0925354254403</v>
       </c>
       <c r="C46" t="n">
         <v>-0.212103999924825</v>
@@ -2064,7 +2064,7 @@
         <v>14</v>
       </c>
       <c r="B57" t="n">
-        <v>37.8924310725676</v>
+        <v>37.8924310725672</v>
       </c>
       <c r="C57" t="n">
         <v>0.00419338370937894</v>
@@ -2116,7 +2116,7 @@
         <v>16</v>
       </c>
       <c r="B59" t="n">
-        <v>38.0919450804004</v>
+        <v>38.0919450803861</v>
       </c>
       <c r="C59" t="n">
         <v>0.0207313021641273</v>
@@ -2246,7 +2246,7 @@
         <v>21</v>
       </c>
       <c r="B64" t="n">
-        <v>38.2883911294841</v>
+        <v>38.2883911294605</v>
       </c>
       <c r="C64" t="n">
         <v>-0.0472074421045568</v>
@@ -2324,7 +2324,7 @@
         <v>24</v>
       </c>
       <c r="B67" t="n">
-        <v>37.9538767889898</v>
+        <v>37.9538767891863</v>
       </c>
       <c r="C67" t="n">
         <v>-0.0195524953341902</v>
@@ -2480,7 +2480,7 @@
         <v>30</v>
       </c>
       <c r="B73" t="n">
-        <v>37.9296323330166</v>
+        <v>37.9296323330092</v>
       </c>
       <c r="C73" t="n">
         <v>-0.40076065151247</v>
@@ -2584,7 +2584,7 @@
         <v>34</v>
       </c>
       <c r="B77" t="n">
-        <v>38.1358611378785</v>
+        <v>38.1358611378717</v>
       </c>
       <c r="C77" t="n">
         <v>-0.0719145881400765</v>
@@ -2740,7 +2740,7 @@
         <v>40</v>
       </c>
       <c r="B83" t="n">
-        <v>38.0343956381725</v>
+        <v>38.0343956381619</v>
       </c>
       <c r="C83" t="n">
         <v>-0.14452857309233</v>
@@ -2818,7 +2818,7 @@
         <v>43</v>
       </c>
       <c r="B86" t="n">
-        <v>37.9617269046748</v>
+        <v>37.9617269046535</v>
       </c>
       <c r="C86" t="n">
         <v>-0.32083570613195</v>
@@ -2844,7 +2844,7 @@
         <v>44</v>
       </c>
       <c r="B87" t="n">
-        <v>38.0162606459222</v>
+        <v>38.0162606458934</v>
       </c>
       <c r="C87" t="n">
         <v>-0.191797476890575</v>
@@ -2870,7 +2870,7 @@
         <v>45</v>
       </c>
       <c r="B88" t="n">
-        <v>38.1637475437495</v>
+        <v>38.1637475437615</v>
       </c>
       <c r="C88" t="n">
         <v>-0.186084816531836</v>
@@ -2896,7 +2896,7 @@
         <v>46</v>
       </c>
       <c r="B89" t="n">
-        <v>38.1155711122823</v>
+        <v>38.1155711122832</v>
       </c>
       <c r="C89" t="n">
         <v>-0.226560786650188</v>
@@ -2948,7 +2948,7 @@
         <v>48</v>
       </c>
       <c r="B91" t="n">
-        <v>38.1808170161058</v>
+        <v>38.1808170161056</v>
       </c>
       <c r="C91" t="n">
         <v>-0.156907838031614</v>
@@ -3000,7 +3000,7 @@
         <v>50</v>
       </c>
       <c r="B93" t="n">
-        <v>37.9445030838813</v>
+        <v>37.9445030838717</v>
       </c>
       <c r="C93" t="n">
         <v>-0.0610734753287546</v>
@@ -3078,7 +3078,7 @@
         <v>53</v>
       </c>
       <c r="B96" t="n">
-        <v>38.0925354254433</v>
+        <v>38.0925354254403</v>
       </c>
       <c r="C96" t="n">
         <v>-0.212103999924825</v>
@@ -3364,7 +3364,7 @@
         <v>14</v>
       </c>
       <c r="B107" t="n">
-        <v>37.8924310725676</v>
+        <v>37.8924310725672</v>
       </c>
       <c r="C107" t="n">
         <v>0.00419338370937894</v>
@@ -3416,7 +3416,7 @@
         <v>16</v>
       </c>
       <c r="B109" t="n">
-        <v>38.0919450804004</v>
+        <v>38.0919450803861</v>
       </c>
       <c r="C109" t="n">
         <v>0.0207313021641273</v>
@@ -3546,7 +3546,7 @@
         <v>21</v>
       </c>
       <c r="B114" t="n">
-        <v>38.2883911294841</v>
+        <v>38.2883911294605</v>
       </c>
       <c r="C114" t="n">
         <v>-0.0472074421045568</v>
@@ -3624,7 +3624,7 @@
         <v>24</v>
       </c>
       <c r="B117" t="n">
-        <v>37.9538767889898</v>
+        <v>37.9538767891863</v>
       </c>
       <c r="C117" t="n">
         <v>-0.0195524953341902</v>
@@ -3780,7 +3780,7 @@
         <v>30</v>
       </c>
       <c r="B123" t="n">
-        <v>37.9296323330166</v>
+        <v>37.9296323330092</v>
       </c>
       <c r="C123" t="n">
         <v>-0.40076065151247</v>
@@ -3884,7 +3884,7 @@
         <v>34</v>
       </c>
       <c r="B127" t="n">
-        <v>38.1358611378785</v>
+        <v>38.1358611378717</v>
       </c>
       <c r="C127" t="n">
         <v>-0.0719145881400765</v>
@@ -4040,7 +4040,7 @@
         <v>40</v>
       </c>
       <c r="B133" t="n">
-        <v>38.0343956381725</v>
+        <v>38.0343956381619</v>
       </c>
       <c r="C133" t="n">
         <v>-0.14452857309233</v>
@@ -4118,7 +4118,7 @@
         <v>43</v>
       </c>
       <c r="B136" t="n">
-        <v>37.9617269046748</v>
+        <v>37.9617269046535</v>
       </c>
       <c r="C136" t="n">
         <v>-0.32083570613195</v>
@@ -4144,7 +4144,7 @@
         <v>44</v>
       </c>
       <c r="B137" t="n">
-        <v>38.0162606459222</v>
+        <v>38.0162606458934</v>
       </c>
       <c r="C137" t="n">
         <v>-0.191797476890575</v>
@@ -4170,7 +4170,7 @@
         <v>45</v>
       </c>
       <c r="B138" t="n">
-        <v>38.1637475437495</v>
+        <v>38.1637475437615</v>
       </c>
       <c r="C138" t="n">
         <v>-0.186084816531836</v>
@@ -4196,7 +4196,7 @@
         <v>46</v>
       </c>
       <c r="B139" t="n">
-        <v>38.1155711122823</v>
+        <v>38.1155711122832</v>
       </c>
       <c r="C139" t="n">
         <v>-0.226560786650188</v>
@@ -4248,7 +4248,7 @@
         <v>48</v>
       </c>
       <c r="B141" t="n">
-        <v>38.1808170161058</v>
+        <v>38.1808170161056</v>
       </c>
       <c r="C141" t="n">
         <v>-0.156907838031614</v>
@@ -4300,7 +4300,7 @@
         <v>50</v>
       </c>
       <c r="B143" t="n">
-        <v>37.9445030838813</v>
+        <v>37.9445030838717</v>
       </c>
       <c r="C143" t="n">
         <v>-0.0610734753287546</v>
@@ -4378,7 +4378,7 @@
         <v>53</v>
       </c>
       <c r="B146" t="n">
-        <v>38.0925354254433</v>
+        <v>38.0925354254403</v>
       </c>
       <c r="C146" t="n">
         <v>-0.212103999924825</v>
@@ -4664,7 +4664,7 @@
         <v>14</v>
       </c>
       <c r="B157" t="n">
-        <v>37.8924310725676</v>
+        <v>37.8924310725672</v>
       </c>
       <c r="C157" t="n">
         <v>0.00419338370937894</v>
@@ -4716,7 +4716,7 @@
         <v>16</v>
       </c>
       <c r="B159" t="n">
-        <v>38.0919450804004</v>
+        <v>38.0919450803861</v>
       </c>
       <c r="C159" t="n">
         <v>0.0207313021641273</v>
@@ -4846,7 +4846,7 @@
         <v>21</v>
       </c>
       <c r="B164" t="n">
-        <v>38.2883911294841</v>
+        <v>38.2883911294605</v>
       </c>
       <c r="C164" t="n">
         <v>-0.0472074421045568</v>
@@ -4924,7 +4924,7 @@
         <v>24</v>
       </c>
       <c r="B167" t="n">
-        <v>37.9538767889898</v>
+        <v>37.9538767891863</v>
       </c>
       <c r="C167" t="n">
         <v>-0.0195524953341902</v>
@@ -5080,7 +5080,7 @@
         <v>30</v>
       </c>
       <c r="B173" t="n">
-        <v>37.9296323330166</v>
+        <v>37.9296323330092</v>
       </c>
       <c r="C173" t="n">
         <v>-0.40076065151247</v>
@@ -5184,7 +5184,7 @@
         <v>34</v>
       </c>
       <c r="B177" t="n">
-        <v>38.1358611378785</v>
+        <v>38.1358611378717</v>
       </c>
       <c r="C177" t="n">
         <v>-0.0719145881400765</v>
@@ -5340,7 +5340,7 @@
         <v>40</v>
       </c>
       <c r="B183" t="n">
-        <v>38.0343956381725</v>
+        <v>38.0343956381619</v>
       </c>
       <c r="C183" t="n">
         <v>-0.14452857309233</v>
@@ -5418,7 +5418,7 @@
         <v>43</v>
       </c>
       <c r="B186" t="n">
-        <v>37.9617269046748</v>
+        <v>37.9617269046535</v>
       </c>
       <c r="C186" t="n">
         <v>-0.32083570613195</v>
@@ -5444,7 +5444,7 @@
         <v>44</v>
       </c>
       <c r="B187" t="n">
-        <v>38.0162606459222</v>
+        <v>38.0162606458934</v>
       </c>
       <c r="C187" t="n">
         <v>-0.191797476890575</v>
@@ -5470,7 +5470,7 @@
         <v>45</v>
       </c>
       <c r="B188" t="n">
-        <v>38.1637475437495</v>
+        <v>38.1637475437615</v>
       </c>
       <c r="C188" t="n">
         <v>-0.186084816531836</v>
@@ -5496,7 +5496,7 @@
         <v>46</v>
       </c>
       <c r="B189" t="n">
-        <v>38.1155711122823</v>
+        <v>38.1155711122832</v>
       </c>
       <c r="C189" t="n">
         <v>-0.226560786650188</v>
@@ -5548,7 +5548,7 @@
         <v>48</v>
       </c>
       <c r="B191" t="n">
-        <v>38.1808170161058</v>
+        <v>38.1808170161056</v>
       </c>
       <c r="C191" t="n">
         <v>-0.156907838031614</v>
@@ -5600,7 +5600,7 @@
         <v>50</v>
       </c>
       <c r="B193" t="n">
-        <v>37.9445030838813</v>
+        <v>37.9445030838717</v>
       </c>
       <c r="C193" t="n">
         <v>-0.0610734753287546</v>
@@ -5678,7 +5678,7 @@
         <v>53</v>
       </c>
       <c r="B196" t="n">
-        <v>38.0925354254433</v>
+        <v>38.0925354254403</v>
       </c>
       <c r="C196" t="n">
         <v>-0.212103999924825</v>

--- a/Dr. Peris/Tharaka_Reference_Labelling_Workbook.xlsx
+++ b/Dr. Peris/Tharaka_Reference_Labelling_Workbook.xlsx
@@ -767,7 +767,7 @@
         <v>37.8924310725672</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00419338370937894</v>
+        <v>0.00419338370985933</v>
       </c>
       <c r="D7" t="n">
         <v>2000</v>
@@ -819,7 +819,7 @@
         <v>38.0919450803861</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0207313021641273</v>
+        <v>0.020731302176814</v>
       </c>
       <c r="D9" t="n">
         <v>2000</v>
@@ -949,7 +949,7 @@
         <v>38.2883911294605</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.0472074421045568</v>
+        <v>-0.0472074420875361</v>
       </c>
       <c r="D14" t="n">
         <v>2000</v>
@@ -1027,7 +1027,7 @@
         <v>37.9538767891863</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.0195524953341902</v>
+        <v>-0.0195524954555676</v>
       </c>
       <c r="D17" t="n">
         <v>2000</v>
@@ -1183,7 +1183,7 @@
         <v>37.9296323330092</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.40076065151247</v>
+        <v>-0.40076065148592</v>
       </c>
       <c r="D23" t="n">
         <v>2000</v>
@@ -1287,7 +1287,7 @@
         <v>38.1358611378717</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0719145881400765</v>
+        <v>-0.0719145881374136</v>
       </c>
       <c r="D27" t="n">
         <v>2000</v>
@@ -1339,7 +1339,7 @@
         <v>38.2173796494406</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0796522021871022</v>
+        <v>-0.0796522021871698</v>
       </c>
       <c r="D29" t="n">
         <v>2000</v>
@@ -1391,7 +1391,7 @@
         <v>37.9206410919466</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0101129949018118</v>
+        <v>0.0101129949018121</v>
       </c>
       <c r="D31" t="n">
         <v>2000</v>
@@ -1443,7 +1443,7 @@
         <v>38.0343956381619</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.14452857309233</v>
+        <v>-0.144528573074203</v>
       </c>
       <c r="D33" t="n">
         <v>2000</v>
@@ -1521,7 +1521,7 @@
         <v>37.9617269046535</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.32083570613195</v>
+        <v>-0.32083570613045</v>
       </c>
       <c r="D36" t="n">
         <v>2000</v>
@@ -1547,7 +1547,7 @@
         <v>38.0162606458934</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.191797476890575</v>
+        <v>-0.191797476565792</v>
       </c>
       <c r="D37" t="n">
         <v>2000</v>
@@ -1573,7 +1573,7 @@
         <v>38.1637475437615</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.186084816531836</v>
+        <v>-0.186084816551405</v>
       </c>
       <c r="D38" t="n">
         <v>2000</v>
@@ -1599,7 +1599,7 @@
         <v>38.1155711122832</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.226560786650188</v>
+        <v>-0.226560786648764</v>
       </c>
       <c r="D39" t="n">
         <v>2000</v>
@@ -1651,7 +1651,7 @@
         <v>38.1808170161056</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.156907838031614</v>
+        <v>-0.156907838031296</v>
       </c>
       <c r="D41" t="n">
         <v>2000</v>
@@ -1703,7 +1703,7 @@
         <v>37.9445030838717</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.0610734753287546</v>
+        <v>-0.0610734752849807</v>
       </c>
       <c r="D43" t="n">
         <v>2000</v>
@@ -1781,7 +1781,7 @@
         <v>38.0925354254403</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.212103999924825</v>
+        <v>-0.212103999917743</v>
       </c>
       <c r="D46" t="n">
         <v>2000</v>
@@ -2067,7 +2067,7 @@
         <v>37.8924310725672</v>
       </c>
       <c r="C57" t="n">
-        <v>0.00419338370937894</v>
+        <v>0.00419338370985933</v>
       </c>
       <c r="D57" t="n">
         <v>2010</v>
@@ -2119,7 +2119,7 @@
         <v>38.0919450803861</v>
       </c>
       <c r="C59" t="n">
-        <v>0.0207313021641273</v>
+        <v>0.020731302176814</v>
       </c>
       <c r="D59" t="n">
         <v>2010</v>
@@ -2249,7 +2249,7 @@
         <v>38.2883911294605</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.0472074421045568</v>
+        <v>-0.0472074420875361</v>
       </c>
       <c r="D64" t="n">
         <v>2010</v>
@@ -2327,7 +2327,7 @@
         <v>37.9538767891863</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.0195524953341902</v>
+        <v>-0.0195524954555676</v>
       </c>
       <c r="D67" t="n">
         <v>2010</v>
@@ -2483,7 +2483,7 @@
         <v>37.9296323330092</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.40076065151247</v>
+        <v>-0.40076065148592</v>
       </c>
       <c r="D73" t="n">
         <v>2010</v>
@@ -2587,7 +2587,7 @@
         <v>38.1358611378717</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.0719145881400765</v>
+        <v>-0.0719145881374136</v>
       </c>
       <c r="D77" t="n">
         <v>2010</v>
@@ -2639,7 +2639,7 @@
         <v>38.2173796494406</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.0796522021871022</v>
+        <v>-0.0796522021871698</v>
       </c>
       <c r="D79" t="n">
         <v>2010</v>
@@ -2691,7 +2691,7 @@
         <v>37.9206410919466</v>
       </c>
       <c r="C81" t="n">
-        <v>0.0101129949018118</v>
+        <v>0.0101129949018121</v>
       </c>
       <c r="D81" t="n">
         <v>2010</v>
@@ -2743,7 +2743,7 @@
         <v>38.0343956381619</v>
       </c>
       <c r="C83" t="n">
-        <v>-0.14452857309233</v>
+        <v>-0.144528573074203</v>
       </c>
       <c r="D83" t="n">
         <v>2010</v>
@@ -2821,7 +2821,7 @@
         <v>37.9617269046535</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.32083570613195</v>
+        <v>-0.32083570613045</v>
       </c>
       <c r="D86" t="n">
         <v>2010</v>
@@ -2847,7 +2847,7 @@
         <v>38.0162606458934</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.191797476890575</v>
+        <v>-0.191797476565792</v>
       </c>
       <c r="D87" t="n">
         <v>2010</v>
@@ -2873,7 +2873,7 @@
         <v>38.1637475437615</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.186084816531836</v>
+        <v>-0.186084816551405</v>
       </c>
       <c r="D88" t="n">
         <v>2010</v>
@@ -2899,7 +2899,7 @@
         <v>38.1155711122832</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.226560786650188</v>
+        <v>-0.226560786648764</v>
       </c>
       <c r="D89" t="n">
         <v>2010</v>
@@ -2951,7 +2951,7 @@
         <v>38.1808170161056</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.156907838031614</v>
+        <v>-0.156907838031296</v>
       </c>
       <c r="D91" t="n">
         <v>2010</v>
@@ -3003,7 +3003,7 @@
         <v>37.9445030838717</v>
       </c>
       <c r="C93" t="n">
-        <v>-0.0610734753287546</v>
+        <v>-0.0610734752849807</v>
       </c>
       <c r="D93" t="n">
         <v>2010</v>
@@ -3081,7 +3081,7 @@
         <v>38.0925354254403</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.212103999924825</v>
+        <v>-0.212103999917743</v>
       </c>
       <c r="D96" t="n">
         <v>2010</v>
@@ -3367,7 +3367,7 @@
         <v>37.8924310725672</v>
       </c>
       <c r="C107" t="n">
-        <v>0.00419338370937894</v>
+        <v>0.00419338370985933</v>
       </c>
       <c r="D107" t="n">
         <v>2020</v>
@@ -3419,7 +3419,7 @@
         <v>38.0919450803861</v>
       </c>
       <c r="C109" t="n">
-        <v>0.0207313021641273</v>
+        <v>0.020731302176814</v>
       </c>
       <c r="D109" t="n">
         <v>2020</v>
@@ -3549,7 +3549,7 @@
         <v>38.2883911294605</v>
       </c>
       <c r="C114" t="n">
-        <v>-0.0472074421045568</v>
+        <v>-0.0472074420875361</v>
       </c>
       <c r="D114" t="n">
         <v>2020</v>
@@ -3627,7 +3627,7 @@
         <v>37.9538767891863</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.0195524953341902</v>
+        <v>-0.0195524954555676</v>
       </c>
       <c r="D117" t="n">
         <v>2020</v>
@@ -3783,7 +3783,7 @@
         <v>37.9296323330092</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.40076065151247</v>
+        <v>-0.40076065148592</v>
       </c>
       <c r="D123" t="n">
         <v>2020</v>
@@ -3887,7 +3887,7 @@
         <v>38.1358611378717</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.0719145881400765</v>
+        <v>-0.0719145881374136</v>
       </c>
       <c r="D127" t="n">
         <v>2020</v>
@@ -3939,7 +3939,7 @@
         <v>38.2173796494406</v>
       </c>
       <c r="C129" t="n">
-        <v>-0.0796522021871022</v>
+        <v>-0.0796522021871698</v>
       </c>
       <c r="D129" t="n">
         <v>2020</v>
@@ -3991,7 +3991,7 @@
         <v>37.9206410919466</v>
       </c>
       <c r="C131" t="n">
-        <v>0.0101129949018118</v>
+        <v>0.0101129949018121</v>
       </c>
       <c r="D131" t="n">
         <v>2020</v>
@@ -4043,7 +4043,7 @@
         <v>38.0343956381619</v>
       </c>
       <c r="C133" t="n">
-        <v>-0.14452857309233</v>
+        <v>-0.144528573074203</v>
       </c>
       <c r="D133" t="n">
         <v>2020</v>
@@ -4121,7 +4121,7 @@
         <v>37.9617269046535</v>
       </c>
       <c r="C136" t="n">
-        <v>-0.32083570613195</v>
+        <v>-0.32083570613045</v>
       </c>
       <c r="D136" t="n">
         <v>2020</v>
@@ -4147,7 +4147,7 @@
         <v>38.0162606458934</v>
       </c>
       <c r="C137" t="n">
-        <v>-0.191797476890575</v>
+        <v>-0.191797476565792</v>
       </c>
       <c r="D137" t="n">
         <v>2020</v>
@@ -4173,7 +4173,7 @@
         <v>38.1637475437615</v>
       </c>
       <c r="C138" t="n">
-        <v>-0.186084816531836</v>
+        <v>-0.186084816551405</v>
       </c>
       <c r="D138" t="n">
         <v>2020</v>
@@ -4199,7 +4199,7 @@
         <v>38.1155711122832</v>
       </c>
       <c r="C139" t="n">
-        <v>-0.226560786650188</v>
+        <v>-0.226560786648764</v>
       </c>
       <c r="D139" t="n">
         <v>2020</v>
@@ -4251,7 +4251,7 @@
         <v>38.1808170161056</v>
       </c>
       <c r="C141" t="n">
-        <v>-0.156907838031614</v>
+        <v>-0.156907838031296</v>
       </c>
       <c r="D141" t="n">
         <v>2020</v>
@@ -4303,7 +4303,7 @@
         <v>37.9445030838717</v>
       </c>
       <c r="C143" t="n">
-        <v>-0.0610734753287546</v>
+        <v>-0.0610734752849807</v>
       </c>
       <c r="D143" t="n">
         <v>2020</v>
@@ -4381,7 +4381,7 @@
         <v>38.0925354254403</v>
       </c>
       <c r="C146" t="n">
-        <v>-0.212103999924825</v>
+        <v>-0.212103999917743</v>
       </c>
       <c r="D146" t="n">
         <v>2020</v>
@@ -4667,7 +4667,7 @@
         <v>37.8924310725672</v>
       </c>
       <c r="C157" t="n">
-        <v>0.00419338370937894</v>
+        <v>0.00419338370985933</v>
       </c>
       <c r="D157" t="n">
         <v>2025</v>
@@ -4719,7 +4719,7 @@
         <v>38.0919450803861</v>
       </c>
       <c r="C159" t="n">
-        <v>0.0207313021641273</v>
+        <v>0.020731302176814</v>
       </c>
       <c r="D159" t="n">
         <v>2025</v>
@@ -4849,7 +4849,7 @@
         <v>38.2883911294605</v>
       </c>
       <c r="C164" t="n">
-        <v>-0.0472074421045568</v>
+        <v>-0.0472074420875361</v>
       </c>
       <c r="D164" t="n">
         <v>2025</v>
@@ -4927,7 +4927,7 @@
         <v>37.9538767891863</v>
       </c>
       <c r="C167" t="n">
-        <v>-0.0195524953341902</v>
+        <v>-0.0195524954555676</v>
       </c>
       <c r="D167" t="n">
         <v>2025</v>
@@ -5083,7 +5083,7 @@
         <v>37.9296323330092</v>
       </c>
       <c r="C173" t="n">
-        <v>-0.40076065151247</v>
+        <v>-0.40076065148592</v>
       </c>
       <c r="D173" t="n">
         <v>2025</v>
@@ -5187,7 +5187,7 @@
         <v>38.1358611378717</v>
       </c>
       <c r="C177" t="n">
-        <v>-0.0719145881400765</v>
+        <v>-0.0719145881374136</v>
       </c>
       <c r="D177" t="n">
         <v>2025</v>
@@ -5239,7 +5239,7 @@
         <v>38.2173796494406</v>
       </c>
       <c r="C179" t="n">
-        <v>-0.0796522021871022</v>
+        <v>-0.0796522021871698</v>
       </c>
       <c r="D179" t="n">
         <v>2025</v>
@@ -5291,7 +5291,7 @@
         <v>37.9206410919466</v>
       </c>
       <c r="C181" t="n">
-        <v>0.0101129949018118</v>
+        <v>0.0101129949018121</v>
       </c>
       <c r="D181" t="n">
         <v>2025</v>
@@ -5343,7 +5343,7 @@
         <v>38.0343956381619</v>
       </c>
       <c r="C183" t="n">
-        <v>-0.14452857309233</v>
+        <v>-0.144528573074203</v>
       </c>
       <c r="D183" t="n">
         <v>2025</v>
@@ -5421,7 +5421,7 @@
         <v>37.9617269046535</v>
       </c>
       <c r="C186" t="n">
-        <v>-0.32083570613195</v>
+        <v>-0.32083570613045</v>
       </c>
       <c r="D186" t="n">
         <v>2025</v>
@@ -5447,7 +5447,7 @@
         <v>38.0162606458934</v>
       </c>
       <c r="C187" t="n">
-        <v>-0.191797476890575</v>
+        <v>-0.191797476565792</v>
       </c>
       <c r="D187" t="n">
         <v>2025</v>
@@ -5473,7 +5473,7 @@
         <v>38.1637475437615</v>
       </c>
       <c r="C188" t="n">
-        <v>-0.186084816531836</v>
+        <v>-0.186084816551405</v>
       </c>
       <c r="D188" t="n">
         <v>2025</v>
@@ -5499,7 +5499,7 @@
         <v>38.1155711122832</v>
       </c>
       <c r="C189" t="n">
-        <v>-0.226560786650188</v>
+        <v>-0.226560786648764</v>
       </c>
       <c r="D189" t="n">
         <v>2025</v>
@@ -5551,7 +5551,7 @@
         <v>38.1808170161056</v>
       </c>
       <c r="C191" t="n">
-        <v>-0.156907838031614</v>
+        <v>-0.156907838031296</v>
       </c>
       <c r="D191" t="n">
         <v>2025</v>
@@ -5603,7 +5603,7 @@
         <v>37.9445030838717</v>
       </c>
       <c r="C193" t="n">
-        <v>-0.0610734753287546</v>
+        <v>-0.0610734752849807</v>
       </c>
       <c r="D193" t="n">
         <v>2025</v>
@@ -5681,7 +5681,7 @@
         <v>38.0925354254403</v>
       </c>
       <c r="C196" t="n">
-        <v>-0.212103999924825</v>
+        <v>-0.212103999917743</v>
       </c>
       <c r="D196" t="n">
         <v>2025</v>
